--- a/files/九龙-九龙塘-皇廷汇.xlsx
+++ b/files/九龙-九龙塘-皇廷汇.xlsx
@@ -750,7 +750,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-21</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-08-17</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -990,7 +990,7 @@
         <is>
           <t>A号屋
 10718呎 (4+房)
-(已售)
+(24年-03月)
 $3.40亿
 $31,722/呎</t>
         </is>
@@ -999,7 +999,7 @@
         <is>
           <t>B号屋
 5845呎 (4+房)
-(已售)
+(23年-08月)
 $2.55亿
 $43,593/呎</t>
         </is>

--- a/files/九龙-九龙塘-皇廷汇.xlsx
+++ b/files/九龙-九龙塘-皇廷汇.xlsx
@@ -184,49 +184,49 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -609,7 +609,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-九龙塘-皇廷汇.xlsx
+++ b/files/九龙-九龙塘-皇廷汇.xlsx
@@ -184,49 +184,49 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -609,7 +609,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
